--- a/cds_files/Utah_CDS_2021-2022.xlsx
+++ b/cds_files/Utah_CDS_2021-2022.xlsx
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.64</v>
+        <v>0.51</v>
       </c>
       <c r="C3" t="n">
-        <v>0.64</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="4">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.36</v>
+        <v>0.49</v>
       </c>
       <c r="C4" t="n">
-        <v>0.36</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="5">
